--- a/KAON_Interview.xlsx
+++ b/KAON_Interview.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Giới thiệu bản thân</t>
   </si>
@@ -31,9 +32,6 @@
   </si>
   <si>
     <t>Nếu trong công việc gặp phải vấn đề bạn chưa làm bao giờ bạn sẽ xử lý như thế nào?</t>
-  </si>
-  <si>
-    <t>Nếu hệ thống không có nhiều tài liệu hướng dẫn thì bạn có làm việc được ko?</t>
   </si>
   <si>
     <t>Trường hợp nếu làm dự án cùng KH thì sẽ phải làm công nghệ mới, bạn sẽ tiếp cận như thế nào trong thời gian ngắn nhất?</t>
@@ -71,6 +69,22 @@
   </si>
   <si>
     <t>Last Question: Do you have any question to us?</t>
+  </si>
+  <si>
+    <t>Nếu hệ thống không có nhiều tài liệu hướng dẫn thì bạn có làm việc được ko? Đưa ra 1 case đã từng làm việc với hệ thống ít tài liệu</t>
+  </si>
+  <si>
+    <t>Good afternoon, My name is Hoang Anh. Tôi là một Software Engineer với hơn 4 năm kinh nghiệm phát triển phần mềm. Tôi có nền tảng vững về OOP, STL, multithreading, smart pointer và có kinh nghiệm xây dựng, bảo trì API cho hệ thống nhúng. Trong quá trình làm việc, tôi thường xuyên debug, build và tối ưu code trên Linux, đồng thời viết Unit Test và Integration Test bằng CMake và Google Test. Tôi đã tham gia các dự án quy mô từ 8–30 người, làm việc theo SDLC và sử dụng CI/CD với Jenkins để đảm bảo chất lượng phần mềm. Tôi quen thuộc với Git, Accurev và có kinh nghiệm quản lý source code trong môi trường dự án lớn. Tôi là người chủ động, có tinh thần trách nhiệm cao và luôn hướng tới việc viết code rõ ràng, ổn định và dễ bảo trì.</t>
+  </si>
+  <si>
+    <t>Good afternoon. My name is Hoang Anh. I am a Software Engineer with over 4 years of experience in software development. I have a strong foundation in OOP, STL, multithreading, multi process and smart pointers, with extensive experience in building and maintaining APIs for embedded systems. In my previous roles, I frequently debugged, built, and optimized code on Linux, while ensuring quality through Unit and Integration Tests using CMake and Google Test. I have collaborated in teams of 8 to 30 members following the SDLC and using CI/CD with Jenkins. I am proficient in Git and Accurev, and experienced in managing source code for large-scale projects. I am a proactive individual with a high sense of responsibility, always aiming to write clean, stable, and maintainable code.</t>
+  </si>
+  <si>
+    <t>Giới thiệu dự án OpenAPI
+Dự án gần đây nhất tôi tham gia là OpenAPI, phát triển tại FPT Software cho máy in đa chức năng Konica Minolta. Mục tiêu của dự án là xây dựng và duy trì API layer bằng C++, cho phép các ứng dụng bên ngoài như Web UI và Mobile App giao tiếp với hệ thống máy in thông qua SOAP protocol.
+Trong dự án này, tôi đảm nhiệm vai trò Developer, tập trung vào phát triển và bảo trì API, xử lý yêu cầu mới từ khách hàng và đảm bảo tính tương thích ngược. Tôi thường xuyên làm việc với specification, review và cập nhật tài liệu kỹ thuật để đảm bảo API hoạt động đúng với yêu cầu hệ thống.
+Về mặt kỹ thuật, tôi code và debug chủ yếu trên Linux, sử dụng C++, STL và các cơ chế xử lý logic hệ thống.Tôi cũng trực tiếp viết Unit Test bằng CMake và Google Test, đồng thời tham gia tạo Integration Test để kiểm tra luồng chức năng end-to-end.
+Ngoài ra, tôi có kinh nghiệm xử lý merge conflict khi tích hợp feature branch, sử dụng Git và làm việc trong môi trường CI/CD với Jenkins. Dự án giúp tôi hiểu rõ hơn cách thiết kế API cho hệ thống embedded, cũng như cách đảm bảo chất lượng code trong một codebase lớn và nhiều người cùng phát triển</t>
   </si>
 </sst>
 </file>
@@ -86,12 +100,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -106,10 +132,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -419,37 +451,37 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -463,7 +495,7 @@
     </row>
     <row r="12" spans="1:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -477,22 +509,22 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -502,4 +534,41 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="D3:I7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="109.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:9" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="4:9" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="4:9" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D7:I7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/KAON_Interview.xlsx
+++ b/KAON_Interview.xlsx
@@ -80,11 +80,7 @@
     <t>Good afternoon. My name is Hoang Anh. I am a Software Engineer with over 4 years of experience in software development. I have a strong foundation in OOP, STL, multithreading, multi process and smart pointers, with extensive experience in building and maintaining APIs for embedded systems. In my previous roles, I frequently debugged, built, and optimized code on Linux, while ensuring quality through Unit and Integration Tests using CMake and Google Test. I have collaborated in teams of 8 to 30 members following the SDLC and using CI/CD with Jenkins. I am proficient in Git and Accurev, and experienced in managing source code for large-scale projects. I am a proactive individual with a high sense of responsibility, always aiming to write clean, stable, and maintainable code.</t>
   </si>
   <si>
-    <t>Giới thiệu dự án OpenAPI
-Dự án gần đây nhất tôi tham gia là OpenAPI, phát triển tại FPT Software cho máy in đa chức năng Konica Minolta. Mục tiêu của dự án là xây dựng và duy trì API layer bằng C++, cho phép các ứng dụng bên ngoài như Web UI và Mobile App giao tiếp với hệ thống máy in thông qua SOAP protocol.
-Trong dự án này, tôi đảm nhiệm vai trò Developer, tập trung vào phát triển và bảo trì API, xử lý yêu cầu mới từ khách hàng và đảm bảo tính tương thích ngược. Tôi thường xuyên làm việc với specification, review và cập nhật tài liệu kỹ thuật để đảm bảo API hoạt động đúng với yêu cầu hệ thống.
-Về mặt kỹ thuật, tôi code và debug chủ yếu trên Linux, sử dụng C++, STL và các cơ chế xử lý logic hệ thống.Tôi cũng trực tiếp viết Unit Test bằng CMake và Google Test, đồng thời tham gia tạo Integration Test để kiểm tra luồng chức năng end-to-end.
-Ngoài ra, tôi có kinh nghiệm xử lý merge conflict khi tích hợp feature branch, sử dụng Git và làm việc trong môi trường CI/CD với Jenkins. Dự án giúp tôi hiểu rõ hơn cách thiết kế API cho hệ thống embedded, cũng như cách đảm bảo chất lượng code trong một codebase lớn và nhiều người cùng phát triển</t>
+    <t>Dự án OpenAPI là dự án gần đây nhất tôi làm, tập trung phát triển và bảo trì API bằng C++ cho máy in đa chức năng. Tôi chủ yếu làm việc với API layer, debug trên Linux, viết Unit Test bằng GTest và xử lý tích hợp code trong môi trường CI/CD. Đây là dự án giúp tôi nắm vững cách phát triển và duy trì code C++ trong hệ thống embedded quy mô lớn.</t>
   </si>
 </sst>
 </file>
@@ -134,14 +130,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -480,32 +476,32 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -545,24 +541,24 @@
   </cols>
   <sheetData>
     <row r="3" spans="4:9" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="4:9" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="4:9" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="1" t="s">
+    <row r="7" spans="4:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/KAON_Interview.xlsx
+++ b/KAON_Interview.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Question" sheetId="1" r:id="rId1"/>
+    <sheet name="Answer" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
   <si>
     <t>Giới thiệu bản thân</t>
   </si>
@@ -80,17 +80,358 @@
     <t>Good afternoon. My name is Hoang Anh. I am a Software Engineer with over 4 years of experience in software development. I have a strong foundation in OOP, STL, multithreading, multi process and smart pointers, with extensive experience in building and maintaining APIs for embedded systems. In my previous roles, I frequently debugged, built, and optimized code on Linux, while ensuring quality through Unit and Integration Tests using CMake and Google Test. I have collaborated in teams of 8 to 30 members following the SDLC and using CI/CD with Jenkins. I am proficient in Git and Accurev, and experienced in managing source code for large-scale projects. I am a proactive individual with a high sense of responsibility, always aiming to write clean, stable, and maintainable code.</t>
   </si>
   <si>
-    <t>Dự án OpenAPI là dự án gần đây nhất tôi làm, tập trung phát triển và bảo trì API bằng C++ cho máy in đa chức năng. Tôi chủ yếu làm việc với API layer, debug trên Linux, viết Unit Test bằng GTest và xử lý tích hợp code trong môi trường CI/CD. Đây là dự án giúp tôi nắm vững cách phát triển và duy trì code C++ trong hệ thống embedded quy mô lớn.</t>
+    <t>The OpenAPI project is my most recent project and passionate about, where I focused on developing and maintaining C++ APIs for multi-function printers. I mainly worked on the API layer, debugged on Linux, and wrote Unit Tests using CMake and GTest. I also handled code integration in a CI/CD environment configured by Jenkins. This project helped me master how to develop and maintain C++ code in large-scale embedded systems.</t>
+  </si>
+  <si>
+    <t>Dự án OpenAPI là dự án gần đây nhất tôi làm và tâm huyết nhất, tập trung phát triển và bảo trì API bằng C++ cho máy in đa chức năng. Tôi chủ yếu làm việc với API layer, debug trên Linux, viết Unit Test bằng CMake kết hợp GTest và xử lý tích hợp code trong môi trường CI/CD, cấu hình bởi Jenkins. Đây là dự án giúp tôi nắm vững cách phát triển và duy trì code C++ trong hệ thống embedded quy mô lớn.</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Why did you change jobs? What were your dissatisfactions with your previous company?</t>
+  </si>
+  <si>
+    <t>Eng</t>
+  </si>
+  <si>
+    <t>Which project are you most passionate about ?</t>
+  </si>
+  <si>
+    <t>Tôi không có điểm gì chưa hài lòng về công ty hiện tại cả. Tôi nghĩ rằng 2 năm cống hiến là đủ để tạo ra giá trị cho công ty hiện tại và nâng cấp kỹ năng bản thân. Giờ đây, tôi cần mở rộng thêm kỹ năng nên tôi quyết định rời đi.</t>
+  </si>
+  <si>
+    <t>I have no dissatisfaction with my current company. I think 2 years of dedication is enough to bring value for my current company and update my pesonal skill. From now, I want to expand my skill in other system. That's why I leave my company</t>
+  </si>
+  <si>
+    <t>Trước tiên, tôi sẽ xác nhận lại rõ yêu cầu và deadline để đưa ra kế hoạch phù hợp. Sau đó tôi sẽ tiến hành tìm hiểu các tài liệu liên quan từ hệ thống lưu trữ của dự án, từ internet và tham khảo ý kiến của đồng nghiệp, techlead.</t>
+  </si>
+  <si>
+    <t>If you encounter a problem at work that you've never dealt with before, how would you handle it?</t>
+  </si>
+  <si>
+    <t>Describe yourself</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">First, I will </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>clarify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>requirements and deadlines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to create a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>suitable plan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Then, I will </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>research relevant documents</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>project's system</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>internet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. I will also </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>consult</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> my </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colleagues</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tech lead</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>for advice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>If the system doesn't have much documentation, can you still work with it? Give a case study of working with a system that has minimal documentation.</t>
+  </si>
+  <si>
+    <t>Trong quá khứ, tôi đã từng làm việc với 1 hệ thống không có nhiều tài liệu hướng dẫn. Khi đó, cách xử lý của tôi là : 
+-Step1 : Đưa ra kế hoạch phù hợp dựa trên yêu cầu
+-Step2 : Study kỹ những tài liệu liên quan đến hệ thống đó
+-Step3 : Tham khảo ý kiến từ đồng nghiệp, tech-lead để implement
+-Step4 : Tạo tài liệu về hệ thống đó, để lưu trữ kinh nghiệm xử lý của bản thân và để sau này người khác dễ tiếp cận hệ thống</t>
+  </si>
+  <si>
+    <t>In the past, I worked on a project with very little documentation. My approach was:
+-Step 1: Create a suitable plan based on the requirements.
+-Step 2: Carefully study all related technical documents of the system.
+-Step 3: Consult my colleagues and tech-lead for advice on the implementation.
+-Step 4: Create new documentation for the system to store my knowledge and help others access the system more easily in the future.</t>
+  </si>
+  <si>
+    <t>If you're working on a project with a client that requires new technology, how would you approach it in the shortest possible time?</t>
+  </si>
+  <si>
+    <t>Trong trường hợp này, tôi nghĩ rằng quan trọng nhất là khả năng tự học hỏi. Tôi sẽ chủ động tìm hiểu tài liệu liên quan tới công nghệ mới đó từ hệ thống lưu trữ manual của dự án và internet, kết hợp với hỗ trợ từ AI. Bên cạnh đó , cũng không kém phần quan trọng, đó là chủ động trao đổi liên tục với những member cùng làm công nghệ mới đó với mình.</t>
+  </si>
+  <si>
+    <t>In this case, I believe the most important factor is self-learning ability. I will proactively research the new technology through project manuals, the internet, and AI assistance. At the same time, it is equally important to maintain continuous communication with team members who are working on the same technology.</t>
+  </si>
+  <si>
+    <t>If you were given a task that you didn't want or didn't like, how would you handle it?</t>
+  </si>
+  <si>
+    <t>Tôi vẫn sẽ nhận task và đảm bảo đúng tiến độ. Tuy nhiên, về hiệu suất lâu dài, thì tôi nghĩ rằng người thích task đó sẽ mang lại hiệu quả cao hơn. Vì vậy, tôi sẽ trình bày với quản lý để được làm task mà phát huy được điểm mạnh của bản thân</t>
+  </si>
+  <si>
+    <t>I will still accept the task and ensure it is finished on schedule. However, regarding long-term performance, I believe that someone who enjoys the task will deliver better results. Therefore, I will discuss this with my manager to be assigned tasks that can best leverage my strengths.</t>
+  </si>
+  <si>
+    <t>How do you resolve conflicts within the team with other members?</t>
+  </si>
+  <si>
+    <t>Nếu là ngoài luồng công việc, tôi thường nhường nhịn và không để xảy ra tranh cãi lớn. Nếu liên quan đến công việc, tôi sẽ list up những ưu, nhược điểm về cách làm của tôi và cách làm của đồng nghiệp đang tranh cãi. Sau đó, cả 2 cùng nhìn nhận lại xem cách nào tốt hơn, có thể để tech lead đánh giá khách quan. Biết đâu có thể gộp được các điểm mạnh từ 2 cách làm.</t>
+  </si>
+  <si>
+    <t>For personal issues, I usually compromise to avoid major arguments. However, for work-related conflicts, I will list the pros and cons of both my approach and my colleague’s. Then, we can review them together or ask the Tech Lead for an objective opinion. We might even find a way to combine the strengths of both ideas.</t>
+  </si>
+  <si>
+    <t>Are you aiming for a technical background or a management career?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -116,7 +457,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -124,11 +465,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -137,10 +494,18 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -419,140 +784,281 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A2:K18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.140625" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="90.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="C9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="C18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A12:J12"/>
-  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C3" location="Answer!C4" display="A1"/>
+    <hyperlink ref="C4" location="Answer!C8" display="A2"/>
+    <hyperlink ref="C5" location="Answer!C12" display="A3"/>
+    <hyperlink ref="C6" location="Answer!C16" display="A4"/>
+    <hyperlink ref="C7" location="Answer!C20" display="A5"/>
+    <hyperlink ref="C8" location="Answer!C24" display="A6"/>
+    <hyperlink ref="C9" location="Answer!C28" display="A7"/>
+    <hyperlink ref="C10" location="Answer!C32" display="A8"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="D3:I7"/>
+  <dimension ref="C3:I32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="109.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:9" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:9" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="4:9" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:9" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
       <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="4:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="3" t="s">
-        <v>18</v>
+    <row r="7" spans="3:9" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -560,10 +1066,93 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
+    <row r="8" spans="3:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="D11" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="D15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="D23" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D27" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D7:I7"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/KAON_Interview.xlsx
+++ b/KAON_Interview.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
   </bookViews>
   <sheets>
     <sheet name="Question" sheetId="1" r:id="rId1"/>
     <sheet name="Answer" sheetId="2" r:id="rId2"/>
+    <sheet name="AnswerTech" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>Giới thiệu bản thân</t>
   </si>
@@ -392,13 +393,59 @@
     <t>How do you resolve conflicts within the team with other members?</t>
   </si>
   <si>
-    <t>Nếu là ngoài luồng công việc, tôi thường nhường nhịn và không để xảy ra tranh cãi lớn. Nếu liên quan đến công việc, tôi sẽ list up những ưu, nhược điểm về cách làm của tôi và cách làm của đồng nghiệp đang tranh cãi. Sau đó, cả 2 cùng nhìn nhận lại xem cách nào tốt hơn, có thể để tech lead đánh giá khách quan. Biết đâu có thể gộp được các điểm mạnh từ 2 cách làm.</t>
-  </si>
-  <si>
-    <t>For personal issues, I usually compromise to avoid major arguments. However, for work-related conflicts, I will list the pros and cons of both my approach and my colleague’s. Then, we can review them together or ask the Tech Lead for an objective opinion. We might even find a way to combine the strengths of both ideas.</t>
-  </si>
-  <si>
     <t>Are you aiming for a technical background or a management career?</t>
+  </si>
+  <si>
+    <t>Tôi định hướng phát triển về technical. Sau 2 năm nữa, tôi muốn trở thành 1 techlead nắm rõ thiết kế hệ thống.</t>
+  </si>
+  <si>
+    <t>For personal matters, I usually compromise or avoid conflicts to keep a good atmosphere. However, for work-related issues, I will list the pros and cons of both my approach and my colleague's. Then, we can review them together or ask the Tech Lead for an objective opinion. We might even find a way to combine the strengths of both ideas.</t>
+  </si>
+  <si>
+    <t>Nếu là ngoài luồng công việc, tôi thường nhường nhịn hoặc lảng tránh để không xảy ra tranh cãi lớn. Nếu liên quan đến công việc, tôi sẽ list up những ưu, nhược điểm về cách làm của tôi và cách làm của đồng nghiệp đang tranh cãi. Sau đó, cả 2 cùng nhìn nhận lại xem cách nào tốt hơn, có thể để tech lead đánh giá khách quan. Biết đâu có thể gộp được các điểm mạnh từ 2 cách làm.</t>
+  </si>
+  <si>
+    <t>I'am aiming for technical background. I see that after 2 year, I will become a module techlead that have a strong knowledge of system design.</t>
+  </si>
+  <si>
+    <t>In your work, do you prefer to receive tasks through the team leader or proactively create tasks to complete?</t>
+  </si>
+  <si>
+    <t>Với tôi, cả 2 điều trên đều OK. Nếu nhận việc qua team lead, tôi sẽ lên kế hoạch và đảm bảo tiến độ. Nếu chủ động tạo task, tôi sẽ confirm trước với team lead về nguyên nhân - đối sách, sau đó tiếp tục các thao tác như điều 1.</t>
+  </si>
+  <si>
+    <t>2 things are OK with me. If I receive tasks from the team lead, I will create a plan and ensure they are finished on schedule. If I proactively create a task, I will first confirm the cause of bug and the solution with the team lead. After that, I will follow the same process as I mentioned before.</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>System call là gì ?</t>
+  </si>
+  <si>
+    <t>AOSP (Android Open Source Project) là mã nguồn mở lõi của hệ điều hành Android. Nó bao gồm các thành phần :
+-System Apps
+-Java API Framework
+-Android Runtime + Native Lib
+-HAL (Hardware Abstraction Layer)
+-Linux Kernel</t>
+  </si>
+  <si>
+    <t>HAL là cầu nối giữa phần cứng và Android Framework</t>
+  </si>
+  <si>
+    <t>Vai trò : HAL sử dụng C++, cung cấp API chuẩn cho :
+Camera
+Audio
+Sensors
+GPS
+Bluetooth</t>
+  </si>
+  <si>
+    <t>System call là cơ chế để chương trình ở user space yêu cầu kernel thực hiện các thao tác đặc quyền, như truy cập file, tạo process, cấp phát bộ nhớ hay giao tiếp với thiết bị phần cứng.</t>
+  </si>
+  <si>
+    <t>A12</t>
   </si>
 </sst>
 </file>
@@ -457,7 +504,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -480,12 +527,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -503,6 +561,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -784,16 +846,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:K19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="81.140625" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="90.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.1796875" customWidth="1"/>
+    <col min="3" max="3" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="90.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
@@ -807,7 +869,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -821,7 +883,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -835,7 +897,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -849,7 +911,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -863,7 +925,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -877,7 +939,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -891,7 +953,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -905,7 +967,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -919,38 +981,44 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:11" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="62" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="D13" s="5"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -960,14 +1028,16 @@
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
-    <row r="14" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>12</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5"/>
+      <c r="B14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>66</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -977,47 +1047,55 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>13</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>11</v>
+      <c r="B15" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1029,6 +1107,10 @@
     <hyperlink ref="C8" location="Answer!C24" display="A6"/>
     <hyperlink ref="C9" location="Answer!C28" display="A7"/>
     <hyperlink ref="C10" location="Answer!C32" display="A8"/>
+    <hyperlink ref="C11" location="Answer!C36" display="A9"/>
+    <hyperlink ref="C12" location="Answer!C40" display="A10"/>
+    <hyperlink ref="C13" location="AnswerTech!B2" display="A11"/>
+    <hyperlink ref="C14" location="AnswerTech!B8" display="A12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1037,18 +1119,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:I32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C3:I41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="109.5703125" customWidth="1"/>
+    <col min="4" max="4" width="109.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:9" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:9" ht="135" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="3:9" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:9" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>23</v>
       </c>
@@ -1056,7 +1138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="3:9" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:9" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1066,7 +1148,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="3:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
         <v>24</v>
       </c>
@@ -1074,12 +1156,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="3:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:9" ht="29" x14ac:dyDescent="0.35">
       <c r="D11" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="3:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:9" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
         <v>25</v>
       </c>
@@ -1087,12 +1169,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="3:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:9" ht="29" x14ac:dyDescent="0.35">
       <c r="D15" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="3:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:9" ht="29" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
         <v>26</v>
       </c>
@@ -1100,12 +1182,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="3:4" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" ht="83.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D19" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="3:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" ht="87" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
         <v>27</v>
       </c>
@@ -1113,12 +1195,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="3:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="D23" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="3:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
         <v>28</v>
       </c>
@@ -1126,12 +1208,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="3:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D27" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="3:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
         <v>29</v>
       </c>
@@ -1139,21 +1221,83 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="3:4" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:4" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D31" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="3:4" ht="45" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C32" t="s">
         <v>30</v>
       </c>
       <c r="D32" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="D35" s="2" t="s">
         <v>53</v>
       </c>
+    </row>
+    <row r="36" spans="3:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="C36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="D39" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="C40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="D41" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="124.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" ht="97" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>